--- a/ISO-9001/ISO-9001-modelo.xlsx
+++ b/ISO-9001/ISO-9001-modelo.xlsx
@@ -3212,11 +3212,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="71208899"/>
-        <c:axId val="38846236"/>
+        <c:axId val="667035"/>
+        <c:axId val="13567041"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="71208899"/>
+        <c:axId val="667035"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3248,7 +3248,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38846236"/>
+        <c:crossAx val="13567041"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3256,7 +3256,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="38846236"/>
+        <c:axId val="13567041"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3296,7 +3296,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71208899"/>
+        <c:crossAx val="667035"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -3692,11 +3692,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="86246838"/>
-        <c:axId val="76412950"/>
+        <c:axId val="83770008"/>
+        <c:axId val="72310626"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="86246838"/>
+        <c:axId val="83770008"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3728,7 +3728,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76412950"/>
+        <c:crossAx val="72310626"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3736,7 +3736,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="76412950"/>
+        <c:axId val="72310626"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3776,7 +3776,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86246838"/>
+        <c:crossAx val="83770008"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -4172,11 +4172,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="25305073"/>
-        <c:axId val="86689033"/>
+        <c:axId val="3006611"/>
+        <c:axId val="16144123"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="25305073"/>
+        <c:axId val="3006611"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -4208,7 +4208,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86689033"/>
+        <c:crossAx val="16144123"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4216,7 +4216,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="86689033"/>
+        <c:axId val="16144123"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4256,7 +4256,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25305073"/>
+        <c:crossAx val="3006611"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>

--- a/ISO-9001/ISO-9001-modelo.xlsx
+++ b/ISO-9001/ISO-9001-modelo.xlsx
@@ -3212,11 +3212,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="667035"/>
-        <c:axId val="13567041"/>
+        <c:axId val="59633425"/>
+        <c:axId val="54757049"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="667035"/>
+        <c:axId val="59633425"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3248,7 +3248,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13567041"/>
+        <c:crossAx val="54757049"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3256,7 +3256,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="13567041"/>
+        <c:axId val="54757049"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3296,7 +3296,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="667035"/>
+        <c:crossAx val="59633425"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -3692,11 +3692,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="83770008"/>
-        <c:axId val="72310626"/>
+        <c:axId val="41469157"/>
+        <c:axId val="92326957"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="83770008"/>
+        <c:axId val="41469157"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3728,7 +3728,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72310626"/>
+        <c:crossAx val="92326957"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3736,7 +3736,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="72310626"/>
+        <c:axId val="92326957"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3776,7 +3776,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83770008"/>
+        <c:crossAx val="41469157"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -4172,11 +4172,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="3006611"/>
-        <c:axId val="16144123"/>
+        <c:axId val="96913825"/>
+        <c:axId val="92690000"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="3006611"/>
+        <c:axId val="96913825"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -4208,7 +4208,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16144123"/>
+        <c:crossAx val="92690000"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4216,7 +4216,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="16144123"/>
+        <c:axId val="92690000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4256,7 +4256,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="3006611"/>
+        <c:crossAx val="96913825"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -7693,16 +7693,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H7:H26 J7:J26" type="date">
+      <formula1>36526</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Número do requisito, como na aba Diagnóstico" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C7:C26" type="list">
       <formula1>"4.1,4.2,4.3,4.4,5.1.1,5.1.2,5.2,5.3,6.1,6.2,6.3,7.1.1,7.1.3,7.1.4,7.1.5,7.1.6,7.2,7.3,7.4,7.5,8.1,8.2.1,8.2.2,8.2.3,8.2.4,8.3,8.4.1,8.4.2,8.4.3,8.5.1,8.5.2,8.5.3,8.5.4,8.5.5,8.5.6,8.6,8.7,9.1.1,9.1.2,9.1.3,9.2,9.3,10.1,10.2,10.3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Não iniciada, Em andamento, Concluída ou Cancelada" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="I7:I26" type="list">
       <formula1>"Não iniciada,Em andamento,Concluída,Cancelada"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H7:H26 J7:J26" type="date">
-      <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/ISO-9001/ISO-9001-modelo.xlsx
+++ b/ISO-9001/ISO-9001-modelo.xlsx
@@ -3212,11 +3212,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="59633425"/>
-        <c:axId val="54757049"/>
+        <c:axId val="97218562"/>
+        <c:axId val="27801338"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="59633425"/>
+        <c:axId val="97218562"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3248,7 +3248,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54757049"/>
+        <c:crossAx val="27801338"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3256,7 +3256,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="54757049"/>
+        <c:axId val="27801338"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3296,7 +3296,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59633425"/>
+        <c:crossAx val="97218562"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -3692,11 +3692,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="41469157"/>
-        <c:axId val="92326957"/>
+        <c:axId val="80925580"/>
+        <c:axId val="92711190"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="41469157"/>
+        <c:axId val="80925580"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3728,7 +3728,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92326957"/>
+        <c:crossAx val="92711190"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3736,7 +3736,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="92326957"/>
+        <c:axId val="92711190"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3776,7 +3776,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41469157"/>
+        <c:crossAx val="80925580"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -4172,11 +4172,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="96913825"/>
-        <c:axId val="92690000"/>
+        <c:axId val="67397486"/>
+        <c:axId val="23364355"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="96913825"/>
+        <c:axId val="67397486"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -4208,7 +4208,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92690000"/>
+        <c:crossAx val="23364355"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4216,7 +4216,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="92690000"/>
+        <c:axId val="23364355"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4256,7 +4256,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96913825"/>
+        <c:crossAx val="67397486"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -7693,16 +7693,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H7:H26 J7:J26" type="date">
-      <formula1>36526</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Número do requisito, como na aba Diagnóstico" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C7:C26" type="list">
       <formula1>"4.1,4.2,4.3,4.4,5.1.1,5.1.2,5.2,5.3,6.1,6.2,6.3,7.1.1,7.1.3,7.1.4,7.1.5,7.1.6,7.2,7.3,7.4,7.5,8.1,8.2.1,8.2.2,8.2.3,8.2.4,8.3,8.4.1,8.4.2,8.4.3,8.5.1,8.5.2,8.5.3,8.5.4,8.5.5,8.5.6,8.6,8.7,9.1.1,9.1.2,9.1.3,9.2,9.3,10.1,10.2,10.3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Não iniciada, Em andamento, Concluída ou Cancelada" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="I7:I26" type="list">
       <formula1>"Não iniciada,Em andamento,Concluída,Cancelada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H7:H26 J7:J26" type="date">
+      <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/ISO-9001/ISO-9001-modelo.xlsx
+++ b/ISO-9001/ISO-9001-modelo.xlsx
@@ -3212,11 +3212,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="97218562"/>
-        <c:axId val="27801338"/>
+        <c:axId val="70520543"/>
+        <c:axId val="40335964"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97218562"/>
+        <c:axId val="70520543"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3248,7 +3248,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27801338"/>
+        <c:crossAx val="40335964"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3256,7 +3256,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="27801338"/>
+        <c:axId val="40335964"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3296,7 +3296,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97218562"/>
+        <c:crossAx val="70520543"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -3692,11 +3692,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="80925580"/>
-        <c:axId val="92711190"/>
+        <c:axId val="74217605"/>
+        <c:axId val="59576086"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="80925580"/>
+        <c:axId val="74217605"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3728,7 +3728,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92711190"/>
+        <c:crossAx val="59576086"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3736,7 +3736,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="92711190"/>
+        <c:axId val="59576086"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3776,7 +3776,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80925580"/>
+        <c:crossAx val="74217605"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -4172,11 +4172,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="67397486"/>
-        <c:axId val="23364355"/>
+        <c:axId val="53032538"/>
+        <c:axId val="71788378"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="67397486"/>
+        <c:axId val="53032538"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -4208,7 +4208,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23364355"/>
+        <c:crossAx val="71788378"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4216,7 +4216,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="23364355"/>
+        <c:axId val="71788378"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4256,7 +4256,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67397486"/>
+        <c:crossAx val="53032538"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>

--- a/ISO-9001/ISO-9001-modelo.xlsx
+++ b/ISO-9001/ISO-9001-modelo.xlsx
@@ -3212,11 +3212,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="70520543"/>
-        <c:axId val="40335964"/>
+        <c:axId val="53475626"/>
+        <c:axId val="18090036"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="70520543"/>
+        <c:axId val="53475626"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3248,7 +3248,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40335964"/>
+        <c:crossAx val="18090036"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3256,7 +3256,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="40335964"/>
+        <c:axId val="18090036"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3296,7 +3296,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70520543"/>
+        <c:crossAx val="53475626"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -3692,11 +3692,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="74217605"/>
-        <c:axId val="59576086"/>
+        <c:axId val="97200023"/>
+        <c:axId val="5983360"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="74217605"/>
+        <c:axId val="97200023"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3728,7 +3728,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59576086"/>
+        <c:crossAx val="5983360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3736,7 +3736,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="59576086"/>
+        <c:axId val="5983360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3776,7 +3776,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74217605"/>
+        <c:crossAx val="97200023"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -4172,11 +4172,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="53032538"/>
-        <c:axId val="71788378"/>
+        <c:axId val="60174096"/>
+        <c:axId val="95958665"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="53032538"/>
+        <c:axId val="60174096"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -4208,7 +4208,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71788378"/>
+        <c:crossAx val="95958665"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4216,7 +4216,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="71788378"/>
+        <c:axId val="95958665"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4256,7 +4256,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53032538"/>
+        <c:crossAx val="60174096"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>

--- a/ISO-9001/ISO-9001-modelo.xlsx
+++ b/ISO-9001/ISO-9001-modelo.xlsx
@@ -3212,11 +3212,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="53475626"/>
-        <c:axId val="18090036"/>
+        <c:axId val="50239947"/>
+        <c:axId val="37491786"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="53475626"/>
+        <c:axId val="50239947"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3248,7 +3248,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18090036"/>
+        <c:crossAx val="37491786"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3256,7 +3256,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="18090036"/>
+        <c:axId val="37491786"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3296,7 +3296,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53475626"/>
+        <c:crossAx val="50239947"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -3692,11 +3692,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="97200023"/>
-        <c:axId val="5983360"/>
+        <c:axId val="74200296"/>
+        <c:axId val="53330837"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97200023"/>
+        <c:axId val="74200296"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3728,7 +3728,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5983360"/>
+        <c:crossAx val="53330837"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3736,7 +3736,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="5983360"/>
+        <c:axId val="53330837"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3776,7 +3776,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97200023"/>
+        <c:crossAx val="74200296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -4172,11 +4172,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="60174096"/>
-        <c:axId val="95958665"/>
+        <c:axId val="71928617"/>
+        <c:axId val="33413043"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="60174096"/>
+        <c:axId val="71928617"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -4208,7 +4208,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95958665"/>
+        <c:crossAx val="33413043"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4216,7 +4216,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="95958665"/>
+        <c:axId val="33413043"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4256,7 +4256,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60174096"/>
+        <c:crossAx val="71928617"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -7693,16 +7693,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H7:H26 J7:J26" type="date">
+      <formula1>36526</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Número do requisito, como na aba Diagnóstico" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C7:C26" type="list">
       <formula1>"4.1,4.2,4.3,4.4,5.1.1,5.1.2,5.2,5.3,6.1,6.2,6.3,7.1.1,7.1.3,7.1.4,7.1.5,7.1.6,7.2,7.3,7.4,7.5,8.1,8.2.1,8.2.2,8.2.3,8.2.4,8.3,8.4.1,8.4.2,8.4.3,8.5.1,8.5.2,8.5.3,8.5.4,8.5.5,8.5.6,8.6,8.7,9.1.1,9.1.2,9.1.3,9.2,9.3,10.1,10.2,10.3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Não iniciada, Em andamento, Concluída ou Cancelada" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="I7:I26" type="list">
       <formula1>"Não iniciada,Em andamento,Concluída,Cancelada"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H7:H26 J7:J26" type="date">
-      <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/ISO-9001/ISO-9001-modelo.xlsx
+++ b/ISO-9001/ISO-9001-modelo.xlsx
@@ -3212,11 +3212,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="50239947"/>
-        <c:axId val="37491786"/>
+        <c:axId val="60108320"/>
+        <c:axId val="58669821"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="50239947"/>
+        <c:axId val="60108320"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3248,7 +3248,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37491786"/>
+        <c:crossAx val="58669821"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3256,7 +3256,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37491786"/>
+        <c:axId val="58669821"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3296,7 +3296,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50239947"/>
+        <c:crossAx val="60108320"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -3692,11 +3692,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="74200296"/>
-        <c:axId val="53330837"/>
+        <c:axId val="89641111"/>
+        <c:axId val="90118626"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="74200296"/>
+        <c:axId val="89641111"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3728,7 +3728,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53330837"/>
+        <c:crossAx val="90118626"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3736,7 +3736,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="53330837"/>
+        <c:axId val="90118626"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3776,7 +3776,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74200296"/>
+        <c:crossAx val="89641111"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -4172,11 +4172,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="71928617"/>
-        <c:axId val="33413043"/>
+        <c:axId val="19199252"/>
+        <c:axId val="9857682"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="71928617"/>
+        <c:axId val="19199252"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -4208,7 +4208,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33413043"/>
+        <c:crossAx val="9857682"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4216,7 +4216,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="33413043"/>
+        <c:axId val="9857682"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4256,7 +4256,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71928617"/>
+        <c:crossAx val="19199252"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -7693,16 +7693,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H7:H26 J7:J26" type="date">
-      <formula1>36526</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Número do requisito, como na aba Diagnóstico" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C7:C26" type="list">
       <formula1>"4.1,4.2,4.3,4.4,5.1.1,5.1.2,5.2,5.3,6.1,6.2,6.3,7.1.1,7.1.3,7.1.4,7.1.5,7.1.6,7.2,7.3,7.4,7.5,8.1,8.2.1,8.2.2,8.2.3,8.2.4,8.3,8.4.1,8.4.2,8.4.3,8.5.1,8.5.2,8.5.3,8.5.4,8.5.5,8.5.6,8.6,8.7,9.1.1,9.1.2,9.1.3,9.2,9.3,10.1,10.2,10.3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Não iniciada, Em andamento, Concluída ou Cancelada" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="I7:I26" type="list">
       <formula1>"Não iniciada,Em andamento,Concluída,Cancelada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H7:H26 J7:J26" type="date">
+      <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/ISO-9001/ISO-9001-modelo.xlsx
+++ b/ISO-9001/ISO-9001-modelo.xlsx
@@ -3212,11 +3212,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="60108320"/>
-        <c:axId val="58669821"/>
+        <c:axId val="24183182"/>
+        <c:axId val="42493779"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="60108320"/>
+        <c:axId val="24183182"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3248,7 +3248,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58669821"/>
+        <c:crossAx val="42493779"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3256,7 +3256,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="58669821"/>
+        <c:axId val="42493779"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3296,7 +3296,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60108320"/>
+        <c:crossAx val="24183182"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -3692,11 +3692,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="89641111"/>
-        <c:axId val="90118626"/>
+        <c:axId val="66956121"/>
+        <c:axId val="91051188"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="89641111"/>
+        <c:axId val="66956121"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3728,7 +3728,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90118626"/>
+        <c:crossAx val="91051188"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3736,7 +3736,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="90118626"/>
+        <c:axId val="91051188"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3776,7 +3776,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89641111"/>
+        <c:crossAx val="66956121"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -4172,11 +4172,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="19199252"/>
-        <c:axId val="9857682"/>
+        <c:axId val="57648159"/>
+        <c:axId val="87882434"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="19199252"/>
+        <c:axId val="57648159"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -4208,7 +4208,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9857682"/>
+        <c:crossAx val="87882434"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4216,7 +4216,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="9857682"/>
+        <c:axId val="87882434"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4256,7 +4256,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19199252"/>
+        <c:crossAx val="57648159"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>

--- a/ISO-9001/ISO-9001-modelo.xlsx
+++ b/ISO-9001/ISO-9001-modelo.xlsx
@@ -3212,11 +3212,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="24183182"/>
-        <c:axId val="42493779"/>
+        <c:axId val="94922281"/>
+        <c:axId val="85654604"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="24183182"/>
+        <c:axId val="94922281"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3248,7 +3248,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42493779"/>
+        <c:crossAx val="85654604"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3256,7 +3256,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="42493779"/>
+        <c:axId val="85654604"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3296,7 +3296,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24183182"/>
+        <c:crossAx val="94922281"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -3692,11 +3692,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="66956121"/>
-        <c:axId val="91051188"/>
+        <c:axId val="33142905"/>
+        <c:axId val="6826028"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="66956121"/>
+        <c:axId val="33142905"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3728,7 +3728,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91051188"/>
+        <c:crossAx val="6826028"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3736,7 +3736,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="91051188"/>
+        <c:axId val="6826028"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3776,7 +3776,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66956121"/>
+        <c:crossAx val="33142905"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -4172,11 +4172,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="57648159"/>
-        <c:axId val="87882434"/>
+        <c:axId val="10042119"/>
+        <c:axId val="17832702"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="57648159"/>
+        <c:axId val="10042119"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -4208,7 +4208,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87882434"/>
+        <c:crossAx val="17832702"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4216,7 +4216,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="87882434"/>
+        <c:axId val="17832702"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4256,7 +4256,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57648159"/>
+        <c:crossAx val="10042119"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>

--- a/ISO-9001/ISO-9001-modelo.xlsx
+++ b/ISO-9001/ISO-9001-modelo.xlsx
@@ -3212,11 +3212,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="94922281"/>
-        <c:axId val="85654604"/>
+        <c:axId val="911016"/>
+        <c:axId val="94122530"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="94922281"/>
+        <c:axId val="911016"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3248,7 +3248,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85654604"/>
+        <c:crossAx val="94122530"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3256,7 +3256,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="85654604"/>
+        <c:axId val="94122530"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3296,7 +3296,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94922281"/>
+        <c:crossAx val="911016"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -3692,11 +3692,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="33142905"/>
-        <c:axId val="6826028"/>
+        <c:axId val="8171689"/>
+        <c:axId val="12236983"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="33142905"/>
+        <c:axId val="8171689"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3728,7 +3728,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6826028"/>
+        <c:crossAx val="12236983"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3736,7 +3736,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="6826028"/>
+        <c:axId val="12236983"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3776,7 +3776,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33142905"/>
+        <c:crossAx val="8171689"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -4172,11 +4172,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="10042119"/>
-        <c:axId val="17832702"/>
+        <c:axId val="46685398"/>
+        <c:axId val="89107729"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="10042119"/>
+        <c:axId val="46685398"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -4208,7 +4208,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17832702"/>
+        <c:crossAx val="89107729"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4216,7 +4216,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="17832702"/>
+        <c:axId val="89107729"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4256,7 +4256,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10042119"/>
+        <c:crossAx val="46685398"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>

--- a/ISO-9001/ISO-9001-modelo.xlsx
+++ b/ISO-9001/ISO-9001-modelo.xlsx
@@ -3212,11 +3212,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="911016"/>
-        <c:axId val="94122530"/>
+        <c:axId val="54370930"/>
+        <c:axId val="22799183"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="911016"/>
+        <c:axId val="54370930"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3248,7 +3248,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94122530"/>
+        <c:crossAx val="22799183"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3256,7 +3256,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94122530"/>
+        <c:axId val="22799183"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3296,7 +3296,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="911016"/>
+        <c:crossAx val="54370930"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -3692,11 +3692,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="8171689"/>
-        <c:axId val="12236983"/>
+        <c:axId val="66195374"/>
+        <c:axId val="61558577"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="8171689"/>
+        <c:axId val="66195374"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3728,7 +3728,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12236983"/>
+        <c:crossAx val="61558577"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3736,7 +3736,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="12236983"/>
+        <c:axId val="61558577"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3776,7 +3776,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8171689"/>
+        <c:crossAx val="66195374"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -4172,11 +4172,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="46685398"/>
-        <c:axId val="89107729"/>
+        <c:axId val="75254078"/>
+        <c:axId val="7464398"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="46685398"/>
+        <c:axId val="75254078"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -4208,7 +4208,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89107729"/>
+        <c:crossAx val="7464398"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4216,7 +4216,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="89107729"/>
+        <c:axId val="7464398"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4256,7 +4256,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46685398"/>
+        <c:crossAx val="75254078"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>

--- a/ISO-9001/ISO-9001-modelo.xlsx
+++ b/ISO-9001/ISO-9001-modelo.xlsx
@@ -3212,11 +3212,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="54370930"/>
-        <c:axId val="22799183"/>
+        <c:axId val="12342977"/>
+        <c:axId val="50859421"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="54370930"/>
+        <c:axId val="12342977"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3248,7 +3248,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22799183"/>
+        <c:crossAx val="50859421"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3256,7 +3256,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="22799183"/>
+        <c:axId val="50859421"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3296,7 +3296,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54370930"/>
+        <c:crossAx val="12342977"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -3692,11 +3692,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="66195374"/>
-        <c:axId val="61558577"/>
+        <c:axId val="85068310"/>
+        <c:axId val="58371430"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="66195374"/>
+        <c:axId val="85068310"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3728,7 +3728,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61558577"/>
+        <c:crossAx val="58371430"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3736,7 +3736,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="61558577"/>
+        <c:axId val="58371430"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3776,7 +3776,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66195374"/>
+        <c:crossAx val="85068310"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -4172,11 +4172,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="75254078"/>
-        <c:axId val="7464398"/>
+        <c:axId val="36418632"/>
+        <c:axId val="84376542"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="75254078"/>
+        <c:axId val="36418632"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -4208,7 +4208,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7464398"/>
+        <c:crossAx val="84376542"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4216,7 +4216,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="7464398"/>
+        <c:axId val="84376542"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4256,7 +4256,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75254078"/>
+        <c:crossAx val="36418632"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>

--- a/ISO-9001/ISO-9001-modelo.xlsx
+++ b/ISO-9001/ISO-9001-modelo.xlsx
@@ -3212,11 +3212,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="12342977"/>
-        <c:axId val="50859421"/>
+        <c:axId val="389711"/>
+        <c:axId val="38235936"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="12342977"/>
+        <c:axId val="389711"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3248,7 +3248,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50859421"/>
+        <c:crossAx val="38235936"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3256,7 +3256,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="50859421"/>
+        <c:axId val="38235936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3296,7 +3296,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12342977"/>
+        <c:crossAx val="389711"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -3692,11 +3692,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="85068310"/>
-        <c:axId val="58371430"/>
+        <c:axId val="5229127"/>
+        <c:axId val="91819015"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="85068310"/>
+        <c:axId val="5229127"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3728,7 +3728,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58371430"/>
+        <c:crossAx val="91819015"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3736,7 +3736,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="58371430"/>
+        <c:axId val="91819015"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3776,7 +3776,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85068310"/>
+        <c:crossAx val="5229127"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -4172,11 +4172,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="36418632"/>
-        <c:axId val="84376542"/>
+        <c:axId val="4927852"/>
+        <c:axId val="37723710"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="36418632"/>
+        <c:axId val="4927852"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -4208,7 +4208,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84376542"/>
+        <c:crossAx val="37723710"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4216,7 +4216,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="84376542"/>
+        <c:axId val="37723710"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4256,7 +4256,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36418632"/>
+        <c:crossAx val="4927852"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>

--- a/ISO-9001/ISO-9001-modelo.xlsx
+++ b/ISO-9001/ISO-9001-modelo.xlsx
@@ -969,7 +969,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="438">
   <si>
     <t xml:space="preserve">ISO 9001 — Como usar esta planilha</t>
   </si>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">Requisitos</t>
   </si>
   <si>
-    <t xml:space="preserve">A lista tem 45 itens. Os requisitos 7.1.1 e 7.1.2 foram reunidos, e os itens dos requisitos 8.3 e 9.3 foram tratados em conjunto. As perguntas e os resumos foram escritos com palavras próprias e não substituem o texto da norma.</t>
+    <t xml:space="preserve">A lista tem 45 itens. Os requisitos 7.1.1 e 7.1.2 foram reunidos. Os subitens de 4.4, 5.2, 6.1, 6.2, 7.1.5, 7.5, 8.2.3, 8.3, 8.7, 9.2, 9.3 e 10.2 foram tratados em conjunto, no requisito de que fazem parte. As perguntas e os resumos foram escritos com palavras próprias e não substituem o texto da norma.</t>
   </si>
   <si>
     <t xml:space="preserve">Percentual</t>
@@ -2024,6 +2024,9 @@
     <t xml:space="preserve">O dono conduz a reunião semanal de indicadores e decide sobre recursos.</t>
   </si>
   <si>
+    <t xml:space="preserve">Escrever a política e conduzir a primeira análise crítica: sem elas, a direção não mostra a política ligada à estratégia nem responde pela eficácia do sistema.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reclamações e entregas no prazo são lidas toda semana pelo dono.</t>
   </si>
   <si>
@@ -2147,7 +2150,7 @@
     <t xml:space="preserve">Bolsa térmica, embalagem lacrada e tempo máximo de espera.</t>
   </si>
   <si>
-    <t xml:space="preserve">Reclamação atendida com reposição ou desconto.</t>
+    <t xml:space="preserve">Garantia da pizza entregue: reposição ou desconto quando ela chega fora do padrão.</t>
   </si>
   <si>
     <t xml:space="preserve">Mudanças de receita e de método não são registradas.</t>
@@ -2234,7 +2237,7 @@
     <t xml:space="preserve">Risco de falta de material crítico identificado.</t>
   </si>
   <si>
-    <t xml:space="preserve">Definir ação para os itens de fornecedor único.</t>
+    <t xml:space="preserve">Definir ação para a resina, de fornecedor único.</t>
   </si>
   <si>
     <t xml:space="preserve">Compradores com treinamento registrado no PR-SUP-01 rev. 5.</t>
@@ -3212,11 +3215,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="389711"/>
-        <c:axId val="38235936"/>
+        <c:axId val="65263753"/>
+        <c:axId val="10671172"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="389711"/>
+        <c:axId val="65263753"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3248,7 +3251,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38235936"/>
+        <c:crossAx val="10671172"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3256,7 +3259,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="38235936"/>
+        <c:axId val="10671172"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3296,7 +3299,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="389711"/>
+        <c:crossAx val="65263753"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -3449,7 +3452,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -3559,7 +3562,7 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>2</c:v>
@@ -3692,11 +3695,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="5229127"/>
-        <c:axId val="91819015"/>
+        <c:axId val="98509694"/>
+        <c:axId val="98948692"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="5229127"/>
+        <c:axId val="98509694"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3728,7 +3731,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91819015"/>
+        <c:crossAx val="98948692"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3736,7 +3739,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="91819015"/>
+        <c:axId val="98948692"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3776,7 +3779,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5229127"/>
+        <c:crossAx val="98509694"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -4172,11 +4175,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="4927852"/>
-        <c:axId val="37723710"/>
+        <c:axId val="77904422"/>
+        <c:axId val="86616538"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="4927852"/>
+        <c:axId val="77904422"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -4208,7 +4211,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37723710"/>
+        <c:crossAx val="86616538"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4216,7 +4219,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37723710"/>
+        <c:axId val="86616538"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4256,7 +4259,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4927852"/>
+        <c:crossAx val="77904422"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -4357,7 +4360,7 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>972000</xdr:colOff>
       <xdr:row>91</xdr:row>
-      <xdr:rowOff>90720</xdr:rowOff>
+      <xdr:rowOff>90360</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4365,7 +4368,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="141120" y="29089440"/>
+        <a:off x="141120" y="29575080"/>
         <a:ext cx="9359640" cy="1871640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -8897,7 +8900,7 @@
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
     </row>
-    <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
         <v>101</v>
       </c>
@@ -8905,17 +8908,19 @@
         <v>102</v>
       </c>
       <c r="D18" s="50" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>350</v>
       </c>
       <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+      <c r="G18" s="7" t="s">
+        <v>351</v>
+      </c>
       <c r="H18" s="7"/>
       <c r="I18" s="21" t="n">
         <f aca="false">IF(D18="Atende",1,IF(D18="Atende em parte",0.5,0))</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J18" s="23" t="n">
         <v>5</v>
@@ -8932,7 +8937,7 @@
         <v>12</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
@@ -8956,11 +8961,11 @@
         <v>16</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="21" t="n">
@@ -8982,7 +8987,7 @@
         <v>12</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
@@ -9018,11 +9023,11 @@
         <v>14</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="21" t="n">
@@ -9044,11 +9049,11 @@
         <v>14</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="21" t="n">
@@ -9070,11 +9075,11 @@
         <v>16</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H25" s="7"/>
       <c r="I25" s="21" t="n">
@@ -9108,7 +9113,7 @@
         <v>12</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
@@ -9132,7 +9137,7 @@
         <v>12</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
@@ -9156,7 +9161,7 @@
         <v>12</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
@@ -9180,11 +9185,11 @@
         <v>14</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="21" t="n">
@@ -9206,11 +9211,11 @@
         <v>14</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="7" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="21" t="n">
@@ -9232,11 +9237,11 @@
         <v>14</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F32" s="7"/>
       <c r="G32" s="7" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="21" t="n">
@@ -9258,11 +9263,11 @@
         <v>14</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F33" s="7"/>
       <c r="G33" s="7" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="21" t="n">
@@ -9284,7 +9289,7 @@
         <v>12</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
@@ -9308,11 +9313,11 @@
         <v>14</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F35" s="7"/>
       <c r="G35" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H35" s="7"/>
       <c r="I35" s="21" t="n">
@@ -9346,7 +9351,7 @@
         <v>12</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
@@ -9370,7 +9375,7 @@
         <v>12</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
@@ -9394,7 +9399,7 @@
         <v>12</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
@@ -9418,11 +9423,11 @@
         <v>14</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F40" s="7"/>
       <c r="G40" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H40" s="7"/>
       <c r="I40" s="21" t="n">
@@ -9444,7 +9449,7 @@
         <v>12</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
@@ -9468,11 +9473,11 @@
         <v>14</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H42" s="7"/>
       <c r="I42" s="21" t="n">
@@ -9494,11 +9499,11 @@
         <v>14</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F43" s="7"/>
       <c r="G43" s="7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="21" t="n">
@@ -9520,7 +9525,7 @@
         <v>12</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
@@ -9544,7 +9549,7 @@
         <v>12</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
@@ -9568,7 +9573,7 @@
         <v>12</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
@@ -9592,7 +9597,7 @@
         <v>12</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
@@ -9616,11 +9621,11 @@
         <v>14</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H48" s="7"/>
       <c r="I48" s="21" t="n">
@@ -9642,7 +9647,7 @@
         <v>12</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="7"/>
@@ -9655,7 +9660,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="47.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="18" t="s">
         <v>191</v>
       </c>
@@ -9666,7 +9671,7 @@
         <v>12</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
@@ -9690,11 +9695,11 @@
         <v>16</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H51" s="7"/>
       <c r="I51" s="21" t="n">
@@ -9716,7 +9721,7 @@
         <v>12</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
@@ -9740,11 +9745,11 @@
         <v>14</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F53" s="7"/>
       <c r="G53" s="7" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H53" s="7"/>
       <c r="I53" s="21" t="n">
@@ -9778,7 +9783,7 @@
         <v>12</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
@@ -9802,11 +9807,11 @@
         <v>14</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F56" s="7"/>
       <c r="G56" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H56" s="7"/>
       <c r="I56" s="21" t="n">
@@ -9828,11 +9833,11 @@
         <v>14</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F57" s="7"/>
       <c r="G57" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H57" s="7"/>
       <c r="I57" s="21" t="n">
@@ -9854,11 +9859,11 @@
         <v>14</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F58" s="7"/>
       <c r="G58" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H58" s="7"/>
       <c r="I58" s="21" t="n">
@@ -9880,11 +9885,11 @@
         <v>16</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F59" s="7"/>
       <c r="G59" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H59" s="7"/>
       <c r="I59" s="21" t="n">
@@ -9918,7 +9923,7 @@
         <v>12</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="7"/>
@@ -9942,11 +9947,11 @@
         <v>14</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F62" s="7"/>
       <c r="G62" s="7" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H62" s="7"/>
       <c r="I62" s="21" t="n">
@@ -9968,7 +9973,7 @@
         <v>12</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F63" s="7"/>
       <c r="G63" s="7"/>
@@ -9983,7 +9988,7 @@
     </row>
     <row r="65" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="17" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C65" s="17"/>
       <c r="D65" s="17"/>
@@ -10068,11 +10073,11 @@
       </c>
       <c r="F68" s="30" t="n">
         <f aca="false">SUMPRODUCT(($J$12:$J$63=5)*($D$12:$D$63="Atende"))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G68" s="30" t="n">
         <f aca="false">SUMPRODUCT(($J$12:$J$63=5)*($D$12:$D$63="Atende em parte"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" s="30" t="n">
         <f aca="false">SUMPRODUCT(($J$12:$J$63=5)*($D$12:$D$63="Não atende"))</f>
@@ -10080,7 +10085,7 @@
       </c>
       <c r="I68" s="31" t="n">
         <f aca="false">IF(E68=0,"",(F68+0.5*G68)/E68)</f>
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10258,11 +10263,11 @@
       </c>
       <c r="F74" s="36" t="n">
         <f aca="false">SUM(F67:F73)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G74" s="36" t="n">
         <f aca="false">SUM(G67:G73)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H74" s="36" t="n">
         <f aca="false">SUM(H67:H73)</f>
@@ -10270,7 +10275,7 @@
       </c>
       <c r="I74" s="31" t="n">
         <f aca="false">IF(E74=0,"",(F74+0.5*G74)/E74)</f>
-        <v>0.677777777777778</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10293,7 +10298,7 @@
       <c r="D77" s="37"/>
       <c r="E77" s="31" t="n">
         <f aca="false">I74</f>
-        <v>0.677777777777778</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="F77" s="31"/>
       <c r="G77" s="31"/>
@@ -10549,7 +10554,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -10565,7 +10570,7 @@
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="48" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E4" s="48"/>
       <c r="F4" s="48"/>
@@ -10593,7 +10598,7 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="48" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E6" s="48"/>
       <c r="F6" s="48"/>
@@ -10607,7 +10612,7 @@
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="48" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E7" s="48"/>
       <c r="F7" s="48"/>
@@ -10621,7 +10626,7 @@
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="48" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E8" s="48"/>
       <c r="F8" s="48"/>
@@ -10635,7 +10640,7 @@
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="48" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E9" s="48"/>
       <c r="F9" s="48"/>
@@ -10691,7 +10696,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
@@ -10727,7 +10732,7 @@
         <v>12</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
@@ -10763,11 +10768,11 @@
         <v>14</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="21" t="n">
@@ -10801,7 +10806,7 @@
         <v>12</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
@@ -10825,7 +10830,7 @@
         <v>12</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
@@ -10861,11 +10866,11 @@
         <v>14</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="21" t="n">
@@ -10887,7 +10892,7 @@
         <v>12</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
@@ -10911,11 +10916,11 @@
         <v>14</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="21" t="n">
@@ -10937,7 +10942,7 @@
         <v>12</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
@@ -10961,7 +10966,7 @@
         <v>12</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
@@ -10997,11 +11002,11 @@
         <v>14</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="21" t="n">
@@ -11023,7 +11028,7 @@
         <v>12</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
@@ -11059,11 +11064,11 @@
         <v>14</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="21" t="n">
@@ -11076,7 +11081,7 @@
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="17" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
@@ -11410,7 +11415,7 @@
     </row>
     <row r="47" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="37" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C47" s="37"/>
       <c r="D47" s="37"/>
